--- a/docs/reference-forms/output/xlsx/TAI-FORM-REF-C008.xlsx
+++ b/docs/reference-forms/output/xlsx/TAI-FORM-REF-C008.xlsx
@@ -10,8 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안전보건 전문인력 평가 기준 및 평가표" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'안전보건 전문인력 평가 기준 및 평가표'!$A$2:$F$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'안전보건 전문인력 평가 기준 및 평가표'!$A$1:$F$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'안전보건 전문인력 평가 기준 및 평가표'!$A$1:$F$293</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -36,6 +35,12 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <i val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
@@ -44,12 +49,6 @@
       <name val="맑은 고딕"/>
       <color rgb="00000000"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <i val="1"/>
-      <color rgb="00000000"/>
-      <sz val="8"/>
     </font>
   </fonts>
   <fills count="6">
@@ -66,17 +65,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FAFAFA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="002F5496"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DCE6F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FAFAFA"/>
       </patternFill>
     </fill>
   </fills>
@@ -104,13 +103,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -186,6 +185,21 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_REF_C008_1" displayName="T_REF_C008_1" ref="A7:F67" headerRowCount="1">
+  <autoFilter ref="A7:F67"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="직책"/>
+    <tableColumn id="2" name="성명"/>
+    <tableColumn id="3" name="담당업무"/>
+    <tableColumn id="4" name="미흡"/>
+    <tableColumn id="5" name="보통"/>
+    <tableColumn id="6" name="양호"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -477,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20.7" customWidth="1" min="1" max="1"/>
@@ -495,324 +509,766 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
+    <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>평가기준</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>양호: 법령에 따른 업무수행으로 수립된 안전보건목표를 달성하고 재해예방에 기여함</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>보통: 법령에 따른 업무를 적정하게 수행함</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>미흡: 법령에 따른 업무를 일부 수행하지 않음</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>* 평가 주기: 반기 1회 이상 평가</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
           <t>직책</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>성명</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>담당업무</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>미흡</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>양호</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="3" t="inlineStr"/>
-      <c r="B4" s="3" t="inlineStr"/>
-      <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="3" t="inlineStr"/>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="3" t="inlineStr"/>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="3" t="inlineStr"/>
-      <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="3" t="inlineStr"/>
-      <c r="B6" s="3" t="inlineStr"/>
-      <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="3" t="inlineStr"/>
-      <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>평가기준</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>양호: 법령에 따른 업무수행으로 수립된 안전보건목표를 달성하고 재해예방에 기여함</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>보통: 법령에 따른 업무를 적정하게 수행함</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>미흡: 법령에 따른 업무를 일부 수행하지 않음</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>* 평가 주기: 반기 1회 이상 평가</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="4" t="inlineStr"/>
+      <c r="B8" s="4" t="inlineStr"/>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="4" t="inlineStr"/>
+      <c r="B9" s="4" t="inlineStr"/>
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="4" t="inlineStr"/>
+      <c r="B10" s="4" t="inlineStr"/>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="4" t="inlineStr"/>
+      <c r="B11" s="4" t="inlineStr"/>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr"/>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="4" t="inlineStr"/>
+      <c r="B12" s="4" t="inlineStr"/>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="4" t="inlineStr"/>
+      <c r="B13" s="4" t="inlineStr"/>
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="4" t="inlineStr"/>
+      <c r="B14" s="4" t="inlineStr"/>
+      <c r="C14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="4" t="inlineStr"/>
+      <c r="B15" s="4" t="inlineStr"/>
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="4" t="inlineStr"/>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4" t="inlineStr"/>
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="4" t="inlineStr"/>
+      <c r="B17" s="4" t="inlineStr"/>
+      <c r="C17" s="4" t="inlineStr"/>
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="4" t="inlineStr"/>
+      <c r="B18" s="4" t="inlineStr"/>
+      <c r="C18" s="4" t="inlineStr"/>
+      <c r="D18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="4" t="inlineStr"/>
+      <c r="B19" s="4" t="inlineStr"/>
+      <c r="C19" s="4" t="inlineStr"/>
+      <c r="D19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="4" t="inlineStr"/>
+      <c r="B20" s="4" t="inlineStr"/>
+      <c r="C20" s="4" t="inlineStr"/>
+      <c r="D20" s="4" t="inlineStr"/>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="4" t="inlineStr"/>
+      <c r="B21" s="4" t="inlineStr"/>
+      <c r="C21" s="4" t="inlineStr"/>
+      <c r="D21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="4" t="inlineStr"/>
+      <c r="B22" s="4" t="inlineStr"/>
+      <c r="C22" s="4" t="inlineStr"/>
+      <c r="D22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="4" t="inlineStr"/>
+      <c r="B23" s="4" t="inlineStr"/>
+      <c r="C23" s="4" t="inlineStr"/>
+      <c r="D23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="4" t="inlineStr"/>
+      <c r="B24" s="4" t="inlineStr"/>
+      <c r="C24" s="4" t="inlineStr"/>
+      <c r="D24" s="4" t="inlineStr"/>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="4" t="inlineStr"/>
+      <c r="B25" s="4" t="inlineStr"/>
+      <c r="C25" s="4" t="inlineStr"/>
+      <c r="D25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="4" t="inlineStr"/>
+      <c r="B26" s="4" t="inlineStr"/>
+      <c r="C26" s="4" t="inlineStr"/>
+      <c r="D26" s="4" t="inlineStr"/>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="4" t="inlineStr"/>
+      <c r="B27" s="4" t="inlineStr"/>
+      <c r="C27" s="4" t="inlineStr"/>
+      <c r="D27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="4" t="inlineStr"/>
+      <c r="B28" s="4" t="inlineStr"/>
+      <c r="C28" s="4" t="inlineStr"/>
+      <c r="D28" s="4" t="inlineStr"/>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="4" t="inlineStr"/>
+      <c r="B29" s="4" t="inlineStr"/>
+      <c r="C29" s="4" t="inlineStr"/>
+      <c r="D29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="4" t="inlineStr"/>
+      <c r="B30" s="4" t="inlineStr"/>
+      <c r="C30" s="4" t="inlineStr"/>
+      <c r="D30" s="4" t="inlineStr"/>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="4" t="inlineStr"/>
+      <c r="B31" s="4" t="inlineStr"/>
+      <c r="C31" s="4" t="inlineStr"/>
+      <c r="D31" s="4" t="inlineStr"/>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="4" t="inlineStr"/>
+      <c r="B32" s="4" t="inlineStr"/>
+      <c r="C32" s="4" t="inlineStr"/>
+      <c r="D32" s="4" t="inlineStr"/>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="4" t="inlineStr"/>
+      <c r="B33" s="4" t="inlineStr"/>
+      <c r="C33" s="4" t="inlineStr"/>
+      <c r="D33" s="4" t="inlineStr"/>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="4" t="inlineStr"/>
+      <c r="B34" s="4" t="inlineStr"/>
+      <c r="C34" s="4" t="inlineStr"/>
+      <c r="D34" s="4" t="inlineStr"/>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="4" t="inlineStr"/>
+      <c r="B35" s="4" t="inlineStr"/>
+      <c r="C35" s="4" t="inlineStr"/>
+      <c r="D35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="4" t="inlineStr"/>
+      <c r="B36" s="4" t="inlineStr"/>
+      <c r="C36" s="4" t="inlineStr"/>
+      <c r="D36" s="4" t="inlineStr"/>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="4" t="inlineStr"/>
+      <c r="B37" s="4" t="inlineStr"/>
+      <c r="C37" s="4" t="inlineStr"/>
+      <c r="D37" s="4" t="inlineStr"/>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="4" t="inlineStr"/>
+      <c r="B38" s="4" t="inlineStr"/>
+      <c r="C38" s="4" t="inlineStr"/>
+      <c r="D38" s="4" t="inlineStr"/>
+      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="4" t="inlineStr"/>
+      <c r="B39" s="4" t="inlineStr"/>
+      <c r="C39" s="4" t="inlineStr"/>
+      <c r="D39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="4" t="inlineStr"/>
+      <c r="B40" s="4" t="inlineStr"/>
+      <c r="C40" s="4" t="inlineStr"/>
+      <c r="D40" s="4" t="inlineStr"/>
+      <c r="E40" s="4" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="4" t="inlineStr"/>
+      <c r="B41" s="4" t="inlineStr"/>
+      <c r="C41" s="4" t="inlineStr"/>
+      <c r="D41" s="4" t="inlineStr"/>
+      <c r="E41" s="4" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="4" t="inlineStr"/>
+      <c r="B42" s="4" t="inlineStr"/>
+      <c r="C42" s="4" t="inlineStr"/>
+      <c r="D42" s="4" t="inlineStr"/>
+      <c r="E42" s="4" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="4" t="inlineStr"/>
+      <c r="B43" s="4" t="inlineStr"/>
+      <c r="C43" s="4" t="inlineStr"/>
+      <c r="D43" s="4" t="inlineStr"/>
+      <c r="E43" s="4" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="4" t="inlineStr"/>
+      <c r="B44" s="4" t="inlineStr"/>
+      <c r="C44" s="4" t="inlineStr"/>
+      <c r="D44" s="4" t="inlineStr"/>
+      <c r="E44" s="4" t="inlineStr"/>
+      <c r="F44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="4" t="inlineStr"/>
+      <c r="B45" s="4" t="inlineStr"/>
+      <c r="C45" s="4" t="inlineStr"/>
+      <c r="D45" s="4" t="inlineStr"/>
+      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr"/>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="4" t="inlineStr"/>
+      <c r="B46" s="4" t="inlineStr"/>
+      <c r="C46" s="4" t="inlineStr"/>
+      <c r="D46" s="4" t="inlineStr"/>
+      <c r="E46" s="4" t="inlineStr"/>
+      <c r="F46" s="4" t="inlineStr"/>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="4" t="inlineStr"/>
+      <c r="B47" s="4" t="inlineStr"/>
+      <c r="C47" s="4" t="inlineStr"/>
+      <c r="D47" s="4" t="inlineStr"/>
+      <c r="E47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr"/>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="4" t="inlineStr"/>
+      <c r="B48" s="4" t="inlineStr"/>
+      <c r="C48" s="4" t="inlineStr"/>
+      <c r="D48" s="4" t="inlineStr"/>
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr"/>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="4" t="inlineStr"/>
+      <c r="B49" s="4" t="inlineStr"/>
+      <c r="C49" s="4" t="inlineStr"/>
+      <c r="D49" s="4" t="inlineStr"/>
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr"/>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="4" t="inlineStr"/>
+      <c r="B50" s="4" t="inlineStr"/>
+      <c r="C50" s="4" t="inlineStr"/>
+      <c r="D50" s="4" t="inlineStr"/>
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr"/>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="4" t="inlineStr"/>
+      <c r="B51" s="4" t="inlineStr"/>
+      <c r="C51" s="4" t="inlineStr"/>
+      <c r="D51" s="4" t="inlineStr"/>
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr"/>
+    </row>
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="4" t="inlineStr"/>
+      <c r="B52" s="4" t="inlineStr"/>
+      <c r="C52" s="4" t="inlineStr"/>
+      <c r="D52" s="4" t="inlineStr"/>
+      <c r="E52" s="4" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr"/>
+    </row>
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="4" t="inlineStr"/>
+      <c r="B53" s="4" t="inlineStr"/>
+      <c r="C53" s="4" t="inlineStr"/>
+      <c r="D53" s="4" t="inlineStr"/>
+      <c r="E53" s="4" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr"/>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="4" t="inlineStr"/>
+      <c r="B54" s="4" t="inlineStr"/>
+      <c r="C54" s="4" t="inlineStr"/>
+      <c r="D54" s="4" t="inlineStr"/>
+      <c r="E54" s="4" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr"/>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="4" t="inlineStr"/>
+      <c r="B55" s="4" t="inlineStr"/>
+      <c r="C55" s="4" t="inlineStr"/>
+      <c r="D55" s="4" t="inlineStr"/>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr"/>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="4" t="inlineStr"/>
+      <c r="B56" s="4" t="inlineStr"/>
+      <c r="C56" s="4" t="inlineStr"/>
+      <c r="D56" s="4" t="inlineStr"/>
+      <c r="E56" s="4" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr"/>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="4" t="inlineStr"/>
+      <c r="B57" s="4" t="inlineStr"/>
+      <c r="C57" s="4" t="inlineStr"/>
+      <c r="D57" s="4" t="inlineStr"/>
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="4" t="inlineStr"/>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="4" t="inlineStr"/>
+      <c r="B58" s="4" t="inlineStr"/>
+      <c r="C58" s="4" t="inlineStr"/>
+      <c r="D58" s="4" t="inlineStr"/>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="4" t="inlineStr"/>
+      <c r="B59" s="4" t="inlineStr"/>
+      <c r="C59" s="4" t="inlineStr"/>
+      <c r="D59" s="4" t="inlineStr"/>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr"/>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="4" t="inlineStr"/>
+      <c r="B60" s="4" t="inlineStr"/>
+      <c r="C60" s="4" t="inlineStr"/>
+      <c r="D60" s="4" t="inlineStr"/>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr"/>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="4" t="inlineStr"/>
+      <c r="B61" s="4" t="inlineStr"/>
+      <c r="C61" s="4" t="inlineStr"/>
+      <c r="D61" s="4" t="inlineStr"/>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr"/>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="4" t="inlineStr"/>
+      <c r="B62" s="4" t="inlineStr"/>
+      <c r="C62" s="4" t="inlineStr"/>
+      <c r="D62" s="4" t="inlineStr"/>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr"/>
+    </row>
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="4" t="inlineStr"/>
+      <c r="B63" s="4" t="inlineStr"/>
+      <c r="C63" s="4" t="inlineStr"/>
+      <c r="D63" s="4" t="inlineStr"/>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr"/>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="4" t="inlineStr"/>
+      <c r="B64" s="4" t="inlineStr"/>
+      <c r="C64" s="4" t="inlineStr"/>
+      <c r="D64" s="4" t="inlineStr"/>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr"/>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="4" t="inlineStr"/>
+      <c r="B65" s="4" t="inlineStr"/>
+      <c r="C65" s="4" t="inlineStr"/>
+      <c r="D65" s="4" t="inlineStr"/>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr"/>
+    </row>
+    <row r="66" ht="16" customHeight="1">
+      <c r="A66" s="4" t="inlineStr"/>
+      <c r="B66" s="4" t="inlineStr"/>
+      <c r="C66" s="4" t="inlineStr"/>
+      <c r="D66" s="4" t="inlineStr"/>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr"/>
+    </row>
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="4" t="inlineStr"/>
+      <c r="B67" s="4" t="inlineStr"/>
+      <c r="C67" s="4" t="inlineStr"/>
+      <c r="D67" s="4" t="inlineStr"/>
+      <c r="E67" s="4" t="inlineStr"/>
+      <c r="F67" s="4" t="inlineStr"/>
+    </row>
+    <row r="68" ht="28" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>【직책별 직무 참조】 (산업안전보건법)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="69" ht="28" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>안전보건관리책임자</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="70" ht="28" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. 사업장의 산재예방계획 수립에 관한 사항</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="71" ht="28" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. 안전보건관리규정(산안법 제25조, 제26조)의 작성 및 변경에 관한 사항</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="72" ht="28" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. 근로자에 대한 안전보건교육(산안법 제29조)에 관한 사항</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="73" ht="28" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. 작업환경의 점검 및 개선에 관한 사항</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="74" ht="28" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  5. 근로자의 건강진단 등 건강관리에 관한 사항</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="75" ht="28" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  6. 산업재해의 원인 조사 및 재발 방지대책 수립에 관한 사항</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="76" ht="28" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  7. 산업재해에 관한 통계의 기록 및 유지관리에 관한 사항</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="77" ht="28" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  8. 안전장치 및 보호구 구입 시 적격품 여부 확인에 관한 사항</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="78" ht="28" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  9. 위험성평가의 실시에 관한 사항</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="79" ht="28" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  10. 안전보건규칙에서 정하는 근로자의 위험 또는 건강장해의 방지에 관한 사항</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="80" ht="28" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>관리감독자</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="81" ht="28" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. 사업장 내 관리감독자가 지휘·감독하는 작업과 관련된 기계·기구 또는 설비의 안전·보건 점검 및 이상 유무의 확인</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="82" ht="28" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. 관리감독자에게 소속된 근로자의 작업복·보호구 및 방호장치의 점검과 그 착용·사용에 관한 교육·지도</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="83" ht="28" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. 해당 작업에서 발생한 산업재해에 관한 보고 및 이에 대한 응급조치</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="84" ht="28" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. 해당 작업의 작업장 정리·정돈 및 통로 확보에 대한 확인·감독</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
+    <row r="85" ht="28" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  5. 안전관리자, 보건관리자, 안전보건관리담당자, 산업보건의의 지도·조언에 대한 협조</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="86" ht="28" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  6. 위험성평가를 위한 유해·위험요인의 파악 및 개선조치 시행에 참여</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="87" ht="28" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>안전보건총괄책임자</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="88" ht="28" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. 위험성평가의 실시에 관한 사항</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="89" ht="28" customHeight="1">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. 산업재해가 발생할 급박한 위험이 있는 경우 및 중대재해 발생 시 작업의 중지</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="90" ht="28" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. 도급 시 산업재해 예방조치</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="91" ht="28" customHeight="1">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. 산업안전보건관리비의 관계수급인 간의 사용에 관한 협의·조정 및 그 집행의 감독</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
+    <row r="92" ht="28" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  5. 안전인증대상기계 등과 자율안전확인대상기계 등의 사용 여부 확인</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:F7"/>
   <mergeCells count="31">
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A84:F84"/>
+    <mergeCell ref="A90:F90"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A75:F75"/>
+    <mergeCell ref="A89:F89"/>
+    <mergeCell ref="A74:F74"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A86:F86"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A71:F71"/>
+    <mergeCell ref="A85:F85"/>
+    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A72:F72"/>
+    <mergeCell ref="A81:F81"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A83:F83"/>
+    <mergeCell ref="A92:F92"/>
+    <mergeCell ref="A77:F77"/>
+    <mergeCell ref="A73:F73"/>
+    <mergeCell ref="A82:F82"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A70:F70"/>
+    <mergeCell ref="A79:F79"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A88:F88"/>
+    <mergeCell ref="A78:F78"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A87:F87"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/docs/reference-forms/output/xlsx/TAI-FORM-REF-C008.xlsx
+++ b/docs/reference-forms/output/xlsx/TAI-FORM-REF-C008.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안전보건 전문인력 평가 기준 및 평가표" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'안전보건 전문인력 평가 기준 및 평가표'!$A$1:$F$293</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'안전보건 전문인력 평가 기준 및 평가표'!$A$1:$F$92</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
